--- a/MainTop/22.09.2026 МПЕ/Москва_p2.xlsx
+++ b/MainTop/22.09.2026 МПЕ/Москва_p2.xlsx
@@ -481,19 +481,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Термобирки Демид</t>
+          <t>Термобирки Дмитрий</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Демид</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Дмитрий</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>1296068698</v>
+        <v>1296053164</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Термобирки Дарья</t>
+          <t>Термобирки Вероника</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Дарья</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вероника</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>1302409355</v>
+        <v>1302408998</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -587,25 +587,25 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Термобирки Даниил</t>
+          <t>Термобирки Влад</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Даниил</t>
+          <t>Термобирки Влад</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>1296053030</v>
+        <v>2365502926</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -643,25 +643,25 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Термобирки Глеб</t>
+          <t>Термобирки Мирослава</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Термобирки Глеб</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослава</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>2365502837</v>
+        <v>1302409296</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -699,25 +699,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Термобирки Павел</t>
+          <t>Термобирки Ксения</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Термобирки Павел</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ксения</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>2365504590</v>
+        <v>1302409277</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -755,25 +755,25 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Термобирки Анастасия</t>
+          <t>Термобирки Алиса</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Анастасия</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Алиса</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>1302409268</v>
+        <v>1302409496</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Термобирки Александра</t>
+          <t>Термобирки Ульяна</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Александра</t>
+          <t>Термобирки Ульяна</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>1302409458</v>
+        <v>2366379751</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -867,25 +867,25 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Термобирки Захар</t>
+          <t>Термобирки Иван</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Термобирки Захар</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Марк</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>2365502448</v>
+        <v>1296050885</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -923,25 +923,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Термобирки Маргарита</t>
+          <t>Термобирки Мария</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Термобирки Маргарита</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мария</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>2366390031</v>
+        <v>1302410399</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -979,25 +979,25 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Термобирки Савелий</t>
+          <t>Термобирки Виктория</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савелий</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Виктория</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>1296068498</v>
+        <v>1302407457</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1035,25 +1035,25 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Термобирки Мирослав</t>
+          <t>Термобирки Василиса</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослав</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Василиса</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>1296069108</v>
+        <v>1302409288</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1091,25 +1091,25 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Термобирки Константин</t>
+          <t>Термобирки Эмилия</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Константин</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Эмилия</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>1296065334</v>
+        <v>1302409040</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1147,25 +1147,25 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Термобирки Екатерина</t>
+          <t>Термобирки Макар</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Екатерина</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Макар</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1302407604</v>
+        <v>1296068268</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1203,25 +1203,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Термобирки Евгений</t>
+          <t>Термобирки Кира</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Евгений</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Кира</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>1296065971</v>
+        <v>1302409262</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1259,25 +1259,25 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Термобирки Давид</t>
+          <t>Термобирки Богдан</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Термобирки Давид</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Богдан</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>2365501731</v>
+        <v>1296068312</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1315,25 +1315,25 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Термобирки Артур</t>
+          <t>Термобирки Анна</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Термобирки Артур</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Анна</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>2365501039</v>
+        <v>1302411737</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1371,25 +1371,25 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Термобирки Ника</t>
+          <t>Термобирки Алексей</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Термобирки Ника</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Алексей</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>2366379865</v>
+        <v>1296065057</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1427,25 +1427,25 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Термобирки Мира</t>
+          <t>Термобирки Аделина</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки одежды в детский сад, именные наклейки, стикеры, бирки. Мира</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Аделина</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>1302410561</v>
+        <v>1302409334</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1483,25 +1483,25 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Термобирки Сергей</t>
+          <t>Термобирки Николай</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Сергей</t>
+          <t>Термобирки Николай</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D20" t="n">
-        <v>1325163089</v>
+        <v>2365501207</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1539,25 +1539,25 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Термобирки Семён</t>
+          <t>Термобирки Есения</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Семён</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Есения</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>1325162457</v>
+        <v>1302409123</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1595,25 +1595,25 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Термобирки Платон</t>
+          <t>Термобирки Демид</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Имя Платон</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Демид</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D22" t="n">
-        <v>1296074062</v>
+        <v>1296068698</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1651,25 +1651,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Термобирки Владимир</t>
+          <t>Термобирки Дарья</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Владимир</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Дарья</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D23" t="n">
-        <v>1325160332</v>
+        <v>1302409355</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Термобирки Виктор</t>
+          <t>Термобирки Даниил</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Термобирки Виктор</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Даниил</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D24" t="n">
-        <v>2365502402</v>
+        <v>1296053030</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1763,25 +1763,25 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Термобирки Вера</t>
+          <t>Термобирки Глеб</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Термобирки Вера</t>
+          <t>Термобирки Глеб</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D25" t="n">
-        <v>2366380729</v>
+        <v>2365502837</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Термобирки Арсений</t>
+          <t>Термобирки Павел</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Термобирки Арсений</t>
+          <t>Термобирки Павел</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
-        <v>2365501953</v>
+        <v>2365504590</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1875,25 +1875,25 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Термобирки Святослав</t>
+          <t>Термобирки Анастасия</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Термобирки Святослав</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Анастасия</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>2365503926</v>
+        <v>1302409268</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1931,25 +1931,25 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Термобирки Марьяна</t>
+          <t>Термобирки Александра</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Термобирки Марьяна</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Александра</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
-        <v>2366379582</v>
+        <v>1302409458</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1987,25 +1987,25 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Термобирки Юрий</t>
+          <t>Термобирки Захар</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юрий</t>
+          <t>Термобирки Захар</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>1296066929</v>
+        <v>2365502448</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2043,25 +2043,25 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Термобирки Степан</t>
+          <t>Термобирки Маргарита</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Степан</t>
+          <t>Термобирки Маргарита</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D30" t="n">
-        <v>1325163507</v>
+        <v>2366390031</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2099,25 +2099,25 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Термобирки Денис</t>
+          <t>Термобирки Савелий</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Денис</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савелий</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>1296066026</v>
+        <v>1296068498</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Термобирки Агата</t>
+          <t>Термобирки Мирослав</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Агата</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослав</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>1302409156</v>
+        <v>1296069108</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2211,25 +2211,25 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Термобирки Любовь</t>
+          <t>Термобирки Константин</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки в детский сад, именные наклейки, бирки. Любовь</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Константин</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>1302418750</v>
+        <v>1296065334</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Термобирки Григорий</t>
+          <t>Термобирки Екатерина</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Термобирки Григорий</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Екатерина</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>2365501184</v>
+        <v>1302407604</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2323,25 +2323,25 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Термобирки Гордей</t>
+          <t>Термобирки Евгений</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Термобирки Гордей</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Евгений</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D35" t="n">
-        <v>2365502823</v>
+        <v>1296065971</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2379,25 +2379,25 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Термобирки Леонид</t>
+          <t>Термобирки Давид</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Термобирки Леонид</t>
+          <t>Термобирки Давид</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>2365501701</v>
+        <v>2365501731</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Термобирки Кристина</t>
+          <t>Термобирки Артур</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Термобирки Кристина</t>
+          <t>Термобирки Артур</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>2366379589</v>
+        <v>2365501039</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2491,25 +2491,25 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Термобирки Фёдор</t>
+          <t>Термобирки Ника</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Фёдор</t>
+          <t>Термобирки Ника</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1296065955</v>
+        <v>2366379865</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2547,25 +2547,25 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Термобирки Оливия</t>
+          <t>Термобирки Мира</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Оливия</t>
+          <t>Термобирки именные для одежды и маркировки одежды в детский сад, именные наклейки, стикеры, бирки. Мира</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>1302409422</v>
+        <v>1302410561</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2603,25 +2603,25 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Термобирки Мухаммад</t>
+          <t>Термобирки Сергей</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мухаммад</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Сергей</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D40" t="n">
-        <v>1296054645</v>
+        <v>1325163089</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2659,25 +2659,25 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Термобирки Лука</t>
+          <t>Термобирки Семён</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Лука</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Семён</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D41" t="n">
-        <v>1296069051</v>
+        <v>1325162457</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2715,25 +2715,25 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Термобирки Леон</t>
+          <t>Термобирки Платон</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Леон</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Имя Платон</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>1296068464</v>
+        <v>1296074062</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2771,25 +2771,25 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Термобирки Игорь</t>
+          <t>Термобирки Владимир</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Игорь</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Владимир</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>1296066808</v>
+        <v>1325160332</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2827,25 +2827,25 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Термобирки Вячеслав</t>
+          <t>Термобирки Виктор</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вячеслав</t>
+          <t>Термобирки Виктор</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D44" t="n">
-        <v>1296067225</v>
+        <v>2365502402</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2883,25 +2883,25 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Термобирки Вадим</t>
+          <t>Термобирки Вера</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вадим</t>
+          <t>Термобирки Вера</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>1296067966</v>
+        <v>2366380729</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2939,25 +2939,25 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Термобирки Адам</t>
+          <t>Термобирки Арсений</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Адам</t>
+          <t>Термобирки Арсений</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D46" t="n">
-        <v>1296068270</v>
+        <v>2365501953</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2995,25 +2995,25 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Термобирки Евгения</t>
+          <t>Термобирки Святослав</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Термобирки Евгения</t>
+          <t>Термобирки Святослав</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>2366379688</v>
+        <v>2365503926</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3051,25 +3051,25 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Термобирки Савва</t>
+          <t>Термобирки Марьяна</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Савва</t>
+          <t>Термобирки Марьяна</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>1296069068</v>
+        <v>2366379582</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3107,25 +3107,25 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Термобирки Ольга</t>
+          <t>Термобирки Юрий</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ольга</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юрий</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>1302408951</v>
+        <v>1296066929</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Термобирки Олег</t>
+          <t>Термобирки Степан</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Олег</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Степан</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>1296067164</v>
+        <v>1325163507</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3219,25 +3219,25 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Термобирки Надежда</t>
+          <t>Термобирки Денис</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Надежда</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Денис</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>1302407720</v>
+        <v>1296066026</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3275,25 +3275,25 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Термобирки Ирина</t>
+          <t>Термобирки Агата</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ирина</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Агата</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>1302407725</v>
+        <v>1302409156</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3331,25 +3331,25 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Термобирки Елена</t>
+          <t>Термобирки Любовь</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Елена</t>
+          <t>Термобирки именные для одежды и маркировки в детский сад, именные наклейки, бирки. Любовь</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>1302409074</v>
+        <v>1302418750</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3387,25 +3387,25 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Термобирки Амалия</t>
+          <t>Термобирки Григорий</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Амалия</t>
+          <t>Термобирки Григорий</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>1302409343</v>
+        <v>2365501184</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3443,25 +3443,25 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Термобирки Владислава</t>
+          <t>Термобирки Гордей</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Термобирки Владислава</t>
+          <t>Термобирки Гордей</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>2366379732</v>
+        <v>2365502823</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3499,25 +3499,25 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Термобирки Юлия</t>
+          <t>Термобирки Леонид</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Юлия</t>
+          <t>Термобирки Леонид</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>1302409546</v>
+        <v>2365501701</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3555,25 +3555,25 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Термобирки Станислав</t>
+          <t>Термобирки Кристина</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Станислав</t>
+          <t>Термобирки Кристина</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>1296067356</v>
+        <v>2366379589</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3611,25 +3611,25 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Термобирки Вениамин</t>
+          <t>Термобирки Фёдор</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Термобирки Вениамин</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Фёдор</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>2365503413</v>
+        <v>1296065955</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Термобирки Аглая</t>
+          <t>Термобирки Оливия</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Термобирки Аглая</t>
+          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Оливия</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59" t="n">
-        <v>2366379897</v>
+        <v>1302409422</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
